--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -662,17 +662,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -724,12 +724,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2828,17 +2828,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
@@ -425,15 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StationID</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Original_Cluster</t>
@@ -508,26 +503,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2905</v>
+        <v>0.2808</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6855</v>
+        <v>0.8186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4176</v>
+        <v>0.1103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2679</v>
+        <v>0.7083</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -535,20 +530,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.0379</v>
+        <v>0.0143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2998</v>
+        <v>0.3771</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6786</v>
+        <v>0.6819</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3788</v>
+        <v>-0.3048</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -558,90 +553,90 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4228</v>
+        <v>0.2111</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9911</v>
+        <v>0.7909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1067</v>
+        <v>0.1763</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8844</v>
+        <v>0.6146</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-0.5142</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0382</v>
+        <v>0.5067</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9882</v>
+        <v>0.6236</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.95</v>
+        <v>-0.1169</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2019</v>
+        <v>0.0094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6468</v>
+        <v>0.5814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.46</v>
+        <v>0.3254</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1868</v>
+        <v>0.256</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,16 +644,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.23</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6982</v>
+        <v>0.4827</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9619</v>
+        <v>0.6382</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2637</v>
+        <v>-0.1555</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -679,43 +674,43 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.925440028538784</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2365</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6641</v>
-      </c>
       <c r="F5" t="n">
-        <v>0.4453</v>
+        <v>0.0309</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2187</v>
+        <v>0.9691</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-0.0799</v>
+        <v>0.026</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6654</v>
+        <v>0.5821</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8929</v>
+        <v>0.3891</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2275</v>
+        <v>0.1931</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -724,38 +719,38 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.886603392782555</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2387</v>
+        <v>0.4513</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9478</v>
+        <v>0.9494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1701</v>
+        <v>0.0402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7776</v>
+        <v>0.9092</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -763,16 +758,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.1098</v>
+        <v>0.1113</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7009</v>
+        <v>0.5939</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2092</v>
+        <v>0.3708</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4917</v>
+        <v>0.2231</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -793,83 +788,83 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5305</v>
+        <v>0.1664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.8162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1154</v>
+        <v>0.0907</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8761</v>
+        <v>0.7255</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2276</v>
+        <v>-0.0994</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7947</v>
+        <v>0.4526</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2132</v>
+        <v>0.6555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5815</v>
+        <v>-0.2029</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.847936693689849</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D8" t="n">
-        <v>0.236</v>
+        <v>0.4107</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149</v>
+        <v>0.9438</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0931</v>
+        <v>0.042</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7217</v>
+        <v>0.9019</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -877,20 +872,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-0.0919</v>
+        <v>0.037</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1934</v>
+        <v>0.0071</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7284</v>
+        <v>0.002</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.535</v>
+        <v>0.0051</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -900,204 +895,204 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.364</v>
+        <v>0.0357</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9959</v>
+        <v>0.8125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1074</v>
+        <v>0.1095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8885</v>
+        <v>0.703</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.1909</v>
+        <v>-0.131</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7105</v>
+        <v>0.4211</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2046</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5058</v>
+        <v>-0.1107</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3921</v>
+        <v>0.2114</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0833</v>
+        <v>0.0746</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7247</v>
+        <v>0.7398</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.0438</v>
+        <v>-0.0508</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2039</v>
+        <v>0.6218</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7244</v>
+        <v>0.7179</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5205</v>
+        <v>-0.0961</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.886603392782555</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5393</v>
+        <v>0.2021</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9919</v>
+        <v>0.8173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1084</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8835</v>
+        <v>0.7187</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.0413</v>
+        <v>-0.0872</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7752</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2325</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5427</v>
+        <v>-0.1305</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4932</v>
+        <v>0.5591</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9944</v>
+        <v>0.884</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1023</v>
+        <v>0.1045</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8921</v>
+        <v>0.7795</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1105,20 +1100,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.1911</v>
+        <v>-0.0211</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7865</v>
+        <v>0.3748</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2181</v>
+        <v>0.6591</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5684</v>
+        <v>-0.2843</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1128,107 +1123,107 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.847936693689849</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1748</v>
+        <v>0.1685</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6813</v>
+        <v>0.8933</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4036</v>
+        <v>0.1462</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2777</v>
+        <v>0.7471</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-0.0034</v>
+        <v>-0.5422</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0493</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0487</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0122</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1595</v>
+        <v>0.5743</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6412</v>
+        <v>0.8913</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4612</v>
+        <v>0.114</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1801</v>
+        <v>0.7773</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-0.0977</v>
+        <v>0.0593</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4679</v>
+        <v>0.635</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6286</v>
+        <v>0.5722</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1607</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1237,55 +1232,55 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4185</v>
+        <v>-0.065</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8062</v>
+        <v>0.742</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0858</v>
+        <v>0.2676</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7204</v>
+        <v>0.4744</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-0.1192</v>
+        <v>-0.1286</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6965</v>
+        <v>0.4866</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9593</v>
+        <v>0.6284</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2628</v>
+        <v>-0.1418</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1294,38 +1289,38 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3176</v>
+        <v>0.353</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9837</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1336</v>
+        <v>0.2947</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8501</v>
+        <v>0.5354</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1333,20 +1328,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.1432</v>
+        <v>-0.0711</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7453</v>
+        <v>0.7019</v>
       </c>
       <c r="K16" t="n">
-        <v>0.219</v>
+        <v>0.6515</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5263</v>
+        <v>0.0504</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1356,33 +1351,33 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1763</v>
+        <v>0.5768</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7059</v>
+        <v>0.8941</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1251</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6262</v>
+        <v>0.769</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1390,16 +1385,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-0.0823</v>
+        <v>0.1248</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3032</v>
+        <v>0.5121</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6806</v>
+        <v>0.4673</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3774</v>
+        <v>0.0448</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1420,26 +1415,26 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5745</v>
+        <v>0.5238</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9893</v>
+        <v>0.8828</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1083</v>
+        <v>0.1069</v>
       </c>
       <c r="G18" t="n">
-        <v>0.881</v>
+        <v>0.7759</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1447,16 +1442,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-0.0136</v>
+        <v>0.0893</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6394</v>
+        <v>0.5115</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3043</v>
+        <v>0.495</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3352</v>
+        <v>0.0164</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1477,43 +1472,43 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1618</v>
+        <v>0.0403</v>
       </c>
       <c r="E19" t="n">
-        <v>0.788</v>
+        <v>0.7542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3017</v>
+        <v>0.2616</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4863</v>
+        <v>0.4926</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-0.0218</v>
+        <v>-0.1463</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8808</v>
+        <v>0.5117</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.5784</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2099</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1522,55 +1517,55 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1139</v>
+        <v>0.5591</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.8883</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4782</v>
+        <v>0.1102</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1574</v>
+        <v>0.7781</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.0053</v>
+        <v>0.0898</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2027</v>
+        <v>0.3944</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7262</v>
+        <v>0.6323</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5236</v>
+        <v>-0.2379</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1579,55 +1574,55 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D21" t="n">
-        <v>0.109</v>
+        <v>0.3056</v>
       </c>
       <c r="E21" t="n">
-        <v>0.62</v>
+        <v>0.8243</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4884</v>
+        <v>0.0858</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1316</v>
+        <v>0.7385</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.0979</v>
+        <v>-0.0462</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3825</v>
+        <v>0.6242</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5915</v>
+        <v>0.7123</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.209</v>
+        <v>-0.0881</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1636,38 +1631,38 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.886603392782555</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5677</v>
+        <v>0.602</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9898</v>
+        <v>0.8884</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1115</v>
+        <v>0.1079</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8783</v>
+        <v>0.7805</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1675,20 +1670,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.078</v>
+        <v>0.0701</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7812</v>
+        <v>0.3953</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2322</v>
+        <v>0.6375</v>
       </c>
       <c r="L22" t="n">
-        <v>0.549</v>
+        <v>-0.2422</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1698,33 +1693,33 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.718546723494759</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1883</v>
+        <v>0.5591</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8149</v>
+        <v>0.8909</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2592</v>
+        <v>0.1089</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5557</v>
+        <v>0.7819</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1732,20 +1727,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.0153</v>
+        <v>0.0751</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9843</v>
+        <v>0.3696</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7178</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2665</v>
+        <v>-0.2892</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1755,50 +1750,50 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1949</v>
+        <v>-0.2465</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8135</v>
+        <v>0.3773</v>
       </c>
       <c r="F24" t="n">
-        <v>0.102</v>
+        <v>0.6827</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7115</v>
+        <v>-0.3054</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.0825</v>
+        <v>-0.1444</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7078</v>
+        <v>0.5298</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9848</v>
+        <v>0.5849</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.277</v>
+        <v>-0.0551</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1807,55 +1802,55 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0313</v>
+        <v>0.0481</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.5787</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4119</v>
+        <v>0.3265</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2873</v>
+        <v>0.2522</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2043</v>
+        <v>0.0325</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.6272</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7117</v>
+        <v>0.7144</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2686</v>
+        <v>-0.0872</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1876,83 +1871,83 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4032</v>
+        <v>0.0951</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7691</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2885</v>
+        <v>0.2384</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4806</v>
+        <v>0.5314</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>-0.2428</v>
+        <v>-0.0205</v>
       </c>
       <c r="J26" t="n">
-        <v>0.705</v>
+        <v>0.6269</v>
       </c>
       <c r="K26" t="n">
-        <v>0.983</v>
+        <v>0.713</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2781</v>
+        <v>-0.0861</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3694</v>
+        <v>0.351</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8109</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0868</v>
+        <v>0.4351</v>
       </c>
       <c r="G27" t="n">
-        <v>0.724</v>
+        <v>0.2448</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1960,16 +1955,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.0219</v>
+        <v>0.0467</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7083</v>
+        <v>0.6976</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9845</v>
+        <v>0.6485</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.2761</v>
+        <v>0.0491</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1990,43 +1985,43 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2394</v>
+        <v>0.0139</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8139</v>
+        <v>0.7982</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1173</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7221</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>-0.0658</v>
+        <v>-0.0319</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7034</v>
+        <v>0.6345</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9627</v>
+        <v>0.7186</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2593</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2035,55 +2030,55 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1017</v>
+        <v>0.5435</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7438</v>
+        <v>0.8929</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1094</v>
+        <v>0.1832</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6343</v>
+        <v>0.7098</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.0648</v>
+        <v>0.1276</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5513</v>
+        <v>0.701</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6066</v>
+        <v>0.6518</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0552</v>
+        <v>0.0492</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2092,55 +2087,55 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4355</v>
+        <v>-0.1228</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7306</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0914</v>
+        <v>0.2852</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7207</v>
+        <v>0.4455</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>-0.0047</v>
+        <v>-0.031</v>
       </c>
       <c r="J30" t="n">
-        <v>0.708</v>
+        <v>0.6341</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9846</v>
+        <v>0.7204</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.2766</v>
+        <v>-0.0863</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2149,38 +2144,38 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3788</v>
+        <v>0.3643</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8119</v>
+        <v>0.8547</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0955</v>
+        <v>0.242</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7164</v>
+        <v>0.6128</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2188,20 +2183,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.0251</v>
+        <v>-0.0168</v>
       </c>
       <c r="J31" t="n">
-        <v>0.708</v>
+        <v>0.6995</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9813</v>
+        <v>0.6511</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.2733</v>
+        <v>0.0484</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2211,33 +2206,33 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4303</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8179</v>
+        <v>0.8894</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0935</v>
+        <v>0.1105</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7244</v>
+        <v>0.7788</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2245,16 +2240,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0677</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6965</v>
+        <v>0.7008</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.6536</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.2507</v>
+        <v>0.0472</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2275,26 +2270,26 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2038</v>
+        <v>0.593</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8119</v>
+        <v>0.8939</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0887</v>
+        <v>0.1081</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7857</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2302,16 +2297,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1376</v>
+        <v>0.0856</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4791</v>
+        <v>0.7016</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4733</v>
+        <v>0.6476</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0058</v>
+        <v>0.054</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2332,26 +2327,26 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.718546723494759</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1559</v>
+        <v>0.4462</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7178</v>
+        <v>0.8488</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2309</v>
+        <v>0.2675</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4869</v>
+        <v>0.5813</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2359,16 +2354,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1402</v>
+        <v>0.0847</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9786</v>
+        <v>0.5068</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7129</v>
+        <v>0.449</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2657</v>
+        <v>0.0578</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2389,43 +2384,43 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4175</v>
+        <v>-0.2638</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8115</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.3004</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7196</v>
+        <v>0.3613</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>-0.14</v>
+        <v>-0.0907</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7064</v>
+        <v>0.4896</v>
       </c>
       <c r="K35" t="n">
-        <v>0.985</v>
+        <v>0.6421</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2787</v>
+        <v>-0.1525</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2434,38 +2429,38 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3285</v>
+        <v>0.5508</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8147</v>
+        <v>0.9061</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1257</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7219</v>
+        <v>0.7804</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2473,16 +2468,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.1125</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7075</v>
+        <v>0.7008</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9845</v>
+        <v>0.6488</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.277</v>
+        <v>0.052</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2503,43 +2498,43 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3613</v>
+        <v>0.1769</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8072</v>
+        <v>0.7936</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7265</v>
+        <v>0.7187</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-0.0725</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7088</v>
+        <v>0.4374</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9848</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.2761</v>
+        <v>-0.1126</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2548,152 +2543,152 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>0.847936693689849</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2678</v>
+        <v>0.1858</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7668</v>
+        <v>0.6246</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2667</v>
+        <v>0.4913</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5001</v>
+        <v>0.1333</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>-0.2208</v>
+        <v>0.0344</v>
       </c>
       <c r="J38" t="n">
-        <v>0.707</v>
+        <v>0.6992</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9843</v>
+        <v>0.6495</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.2773</v>
+        <v>0.0497</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3143</v>
+        <v>0.1475</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8089</v>
+        <v>0.8238</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1058</v>
+        <v>0.0988</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.725</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>-0.1101</v>
+        <v>-0.0316</v>
       </c>
       <c r="J39" t="n">
-        <v>0.71</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9842</v>
+        <v>0.7145</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.2742</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1037</v>
+        <v>0.2104</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.8185</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4432</v>
+        <v>0.0863</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2246</v>
+        <v>0.7322</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2701,16 +2696,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>-0.0595</v>
+        <v>-0.0139</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7093</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9843</v>
+        <v>0.7121</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.2751</v>
+        <v>-0.0916</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2731,43 +2726,43 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1714</v>
+        <v>-0.1252</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7024</v>
+        <v>0.8027</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2664</v>
+        <v>0.1413</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4359</v>
+        <v>0.6614</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.177</v>
+        <v>0.0033</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9858</v>
+        <v>0.6288</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7179</v>
+        <v>0.7169</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2679</v>
+        <v>-0.0881</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2776,55 +2771,55 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0935</v>
+        <v>0.2368</v>
       </c>
       <c r="E42" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.1597</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.0199</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="K42" t="n">
         <v>0.681</v>
       </c>
-      <c r="F42" t="n">
-        <v>0.1042</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.5768</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Peripheral</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>-0.2816</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.7062</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.9854000000000001</v>
-      </c>
       <c r="L42" t="n">
-        <v>-0.2793</v>
+        <v>-0.2694</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2845,26 +2840,26 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.718546723494759</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.066</v>
+        <v>-0.1229</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5572</v>
+        <v>0.4688</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4249</v>
+        <v>0.6168</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1324</v>
+        <v>-0.148</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2872,16 +2867,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.2006</v>
+        <v>-0.0306</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9826</v>
+        <v>0.6278</v>
       </c>
       <c r="K43" t="n">
-        <v>0.715</v>
+        <v>0.7141</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2676</v>
+        <v>-0.0863</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2896,462 +2891,6 @@
       <c r="O43" t="inlineStr">
         <is>
           <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.3467</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.8036</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.0838</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.7198</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>-0.0955</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.7094</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.9841</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-0.2747</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.7883</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.3196</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.4687</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Peripheral</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.9831</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.7167</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.2664</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.7723</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.3219</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.4504</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Peripheral</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.1245</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.7151999999999999</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.2657</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.2219</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.7446</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.5173</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.1703</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.7163</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.2672</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.718546723494759</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.8227</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.2406</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.5821</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.9709</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.7114</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.2594</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.3445</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.7147</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.3874</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.3272</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>-0.0443</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.6994</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.9335</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-0.2341</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.3575</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.8052</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.07920000000000001</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>-0.0898</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.7065</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.9831</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-0.2765</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.847936693689849</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.3168</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.6819</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.4178</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>-0.0566</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-0.533</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,19 +510,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2808</v>
+        <v>0.3202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8186</v>
+        <v>0.8939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1103</v>
+        <v>0.0074</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7083</v>
+        <v>0.8865</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -530,20 +530,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.0143</v>
+        <v>0.0533</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3771</v>
+        <v>0.767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6819</v>
+        <v>0.5633</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3048</v>
+        <v>0.2037</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -553,33 +553,33 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2111</v>
+        <v>0.2267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7909</v>
+        <v>0.8777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1763</v>
+        <v>0.0303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6146</v>
+        <v>0.8474</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5067</v>
+        <v>0.7891</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6236</v>
+        <v>0.6081</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1169</v>
+        <v>0.181</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -617,83 +617,83 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0094</v>
+        <v>-0.0713</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5814</v>
+        <v>0.7866</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3254</v>
+        <v>0.3453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.256</v>
+        <v>0.4413</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1175</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4827</v>
+        <v>0.1075</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6382</v>
+        <v>0.438</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1555</v>
+        <v>-0.3305</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.925440028538784</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3885</v>
+        <v>0.2942</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0309</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9691</v>
+        <v>0.8867</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.026</v>
+        <v>0.1654</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5821</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3891</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1931</v>
+        <v>0.2086</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -731,43 +731,43 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.925440028538784</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4513</v>
+        <v>0.1115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9494</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0402</v>
+        <v>0.0898</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9092</v>
+        <v>0.7827</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.1113</v>
+        <v>0.3912</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5939</v>
+        <v>0.6092</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3708</v>
+        <v>0.1602</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2231</v>
+        <v>0.449</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -776,112 +776,112 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1664</v>
+        <v>-0.1004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8162</v>
+        <v>0.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0907</v>
+        <v>0.7847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7255</v>
+        <v>-0.5806</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.0994</v>
+        <v>0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4526</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6555</v>
+        <v>0.6135</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2029</v>
+        <v>0.1924</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.925440028538784</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4107</v>
+        <v>0.1032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9438</v>
+        <v>0.9091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.042</v>
+        <v>0.161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9019</v>
+        <v>0.7481</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.037</v>
+        <v>0.2896</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0071</v>
+        <v>0.6097</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002</v>
+        <v>0.1753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0051</v>
+        <v>0.4343</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -890,38 +890,38 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0357</v>
+        <v>0.2234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8125</v>
+        <v>0.8088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1095</v>
+        <v>0.0672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.703</v>
+        <v>0.7416</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -929,56 +929,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-0.131</v>
+        <v>0.0011</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4211</v>
+        <v>0.0342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.0954</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1107</v>
+        <v>-0.0612</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2114</v>
+        <v>0.1956</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8144</v>
+        <v>0.7721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0746</v>
+        <v>0.1134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7398</v>
+        <v>0.6587</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -986,20 +986,20 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.0508</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6218</v>
+        <v>0.2273</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7179</v>
+        <v>0.339</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0961</v>
+        <v>-0.1117</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1009,90 +1009,90 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2021</v>
+        <v>0.444</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8173</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7187</v>
+        <v>0.8872</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.0872</v>
+        <v>-0.0052</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.7438</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.7328</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1305</v>
+        <v>0.011</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5591</v>
+        <v>0.4431</v>
       </c>
       <c r="E12" t="n">
-        <v>0.884</v>
+        <v>0.8972</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1045</v>
+        <v>0.0073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7795</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1100,20 +1100,20 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-0.0211</v>
+        <v>0.2501</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3748</v>
+        <v>0.8089</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6591</v>
+        <v>0.5981</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2843</v>
+        <v>0.2108</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1123,33 +1123,33 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.925440028538784</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1685</v>
+        <v>0.1635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8933</v>
+        <v>0.9241</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1462</v>
+        <v>0.1859</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7471</v>
+        <v>0.7382</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-0.5422</v>
+        <v>-0.1441</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.1031</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.7383</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0122</v>
+        <v>-0.6352</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1187,140 +1187,140 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.96404592749758</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5743</v>
+        <v>0.0428</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8913</v>
+        <v>0.7708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.114</v>
+        <v>0.3052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7773</v>
+        <v>0.4656</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.0593</v>
+        <v>-0.4039</v>
       </c>
       <c r="J14" t="n">
-        <v>0.635</v>
+        <v>0.0342</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5722</v>
+        <v>0.6692</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.635</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.065</v>
+        <v>0.449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.742</v>
+        <v>0.8937</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2676</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4744</v>
+        <v>0.8858</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-0.1286</v>
+        <v>-0.0159</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4866</v>
+        <v>0.7901</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6284</v>
+        <v>0.6409</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1418</v>
+        <v>0.1491</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D16" t="n">
-        <v>0.353</v>
+        <v>0.2812</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2947</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5354</v>
+        <v>0.8861</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-0.0711</v>
+        <v>-0.1076</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7019</v>
+        <v>0.6994</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6515</v>
+        <v>0.7371</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0504</v>
+        <v>-0.0377</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1358,43 +1358,43 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.96404592749758</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5768</v>
+        <v>0.1556</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8941</v>
+        <v>0.9142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1251</v>
+        <v>0.1014</v>
       </c>
       <c r="G17" t="n">
-        <v>0.769</v>
+        <v>0.8128</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.1248</v>
+        <v>0.2777</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5121</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4673</v>
+        <v>0.1628</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0448</v>
+        <v>0.4415</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1403,38 +1403,38 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5238</v>
+        <v>0.3595</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8828</v>
+        <v>0.8949</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1069</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7759</v>
+        <v>0.8869</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.0893</v>
+        <v>0.1534</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5115</v>
+        <v>0.8001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.495</v>
+        <v>0.6466</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0164</v>
+        <v>0.1534</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1472,43 +1472,43 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0403</v>
+        <v>0.3168</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7542</v>
+        <v>0.9093</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2616</v>
+        <v>0.0496</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4926</v>
+        <v>0.8597</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-0.1463</v>
+        <v>0.3124</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5117</v>
+        <v>0.6056</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5784</v>
+        <v>0.1604</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.4452</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1517,112 +1517,112 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5591</v>
+        <v>0.2357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8883</v>
+        <v>0.8474</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1102</v>
+        <v>0.0323</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7781</v>
+        <v>0.8151</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.0898</v>
+        <v>0.1401</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3944</v>
+        <v>0.8038</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6323</v>
+        <v>0.626</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2379</v>
+        <v>0.1778</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3056</v>
+        <v>0.1873</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8243</v>
+        <v>0.7983</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0858</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7385</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.0462</v>
+        <v>0.0391</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6242</v>
+        <v>0.7163</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7123</v>
+        <v>0.7359</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0881</v>
+        <v>-0.0197</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1631,55 +1631,55 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D22" t="n">
-        <v>0.602</v>
+        <v>0.221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8884</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1079</v>
+        <v>0.0599</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7805</v>
+        <v>0.7623</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.0701</v>
+        <v>-0.1993</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3953</v>
+        <v>0.2439</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6375</v>
+        <v>0.379</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2422</v>
+        <v>-0.135</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1688,38 +1688,38 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5591</v>
+        <v>0.4601</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8909</v>
+        <v>0.8948</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1089</v>
+        <v>0.0071</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7819</v>
+        <v>0.8877</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1727,20 +1727,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.0751</v>
+        <v>0.2256</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3696</v>
+        <v>0.8017</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2892</v>
+        <v>0.2165</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1750,50 +1750,50 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2465</v>
+        <v>0.4298</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3773</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6827</v>
+        <v>0.0077</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3054</v>
+        <v>0.8879</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-0.1444</v>
+        <v>0.2116</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5298</v>
+        <v>0.8038</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5849</v>
+        <v>0.5898</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0551</v>
+        <v>0.214</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1802,38 +1802,38 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0481</v>
+        <v>0.2427</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5787</v>
+        <v>0.8931</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3265</v>
+        <v>0.0083</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2522</v>
+        <v>0.8848</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.0325</v>
+        <v>0.098</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6272</v>
+        <v>0.78</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7144</v>
+        <v>0.5702</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0872</v>
+        <v>0.2098</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1871,43 +1871,43 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0951</v>
+        <v>0.4728</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.8951</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2384</v>
+        <v>0.0065</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5314</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>-0.0205</v>
+        <v>0.226</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6269</v>
+        <v>0.8101</v>
       </c>
       <c r="K26" t="n">
-        <v>0.713</v>
+        <v>0.6031</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0861</v>
+        <v>0.207</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1916,38 +1916,38 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D27" t="n">
-        <v>0.351</v>
+        <v>0.3781</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.8758</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4351</v>
+        <v>0.0155</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2448</v>
+        <v>0.8602</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1955,16 +1955,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.0467</v>
+        <v>0.1858</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6976</v>
+        <v>0.7867</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6485</v>
+        <v>0.5759</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0491</v>
+        <v>0.2109</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1985,26 +1985,26 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0139</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7982</v>
+        <v>0.9004</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1173</v>
+        <v>0.1176</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2012,16 +2012,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>-0.0319</v>
+        <v>0.0258</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6345</v>
+        <v>0.2457</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7186</v>
+        <v>0.251</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2042,26 +2042,26 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5435</v>
+        <v>0.4393</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8929</v>
+        <v>0.8939</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1832</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7098</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.1276</v>
+        <v>0.2119</v>
       </c>
       <c r="J29" t="n">
-        <v>0.701</v>
+        <v>0.8062</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6518</v>
+        <v>0.5926</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0492</v>
+        <v>0.2136</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2099,43 +2099,43 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1228</v>
+        <v>0.3796</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7306</v>
+        <v>0.891</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2852</v>
+        <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4455</v>
+        <v>0.8809</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>-0.031</v>
+        <v>0.2374</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6341</v>
+        <v>0.8038</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7204</v>
+        <v>0.5894</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0863</v>
+        <v>0.2144</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2144,38 +2144,38 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3643</v>
+        <v>0.3991</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8547</v>
+        <v>0.8956</v>
       </c>
       <c r="F31" t="n">
-        <v>0.242</v>
+        <v>0.0086</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6128</v>
+        <v>0.887</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2183,20 +2183,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>-0.0168</v>
+        <v>0.2107</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6995</v>
+        <v>0.8058</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6511</v>
+        <v>0.5946</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0484</v>
+        <v>0.2112</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2206,33 +2206,33 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.3534</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8894</v>
+        <v>0.8966</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1105</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7788</v>
+        <v>0.8873</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.0677</v>
+        <v>0.03</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7008</v>
+        <v>0.7996</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6536</v>
+        <v>0.6478</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0472</v>
+        <v>0.1519</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2270,43 +2270,43 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D33" t="n">
-        <v>0.593</v>
+        <v>0.1775</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8939</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1081</v>
+        <v>0.3974</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7857</v>
+        <v>0.1103</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.0856</v>
+        <v>0.0674</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7016</v>
+        <v>0.7679</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6476</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>0.054</v>
+        <v>0.0789</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2315,38 +2315,38 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4462</v>
+        <v>0.4566</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8488</v>
+        <v>0.8951</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2675</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5813</v>
+        <v>0.8871</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.0847</v>
+        <v>0.0936</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5068</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.449</v>
+        <v>0.6142</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0578</v>
+        <v>0.1928</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2384,43 +2384,43 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2638</v>
+        <v>0.3339</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.8862</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3004</v>
+        <v>0.0207</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3613</v>
+        <v>0.8655</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>-0.0907</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4896</v>
+        <v>0.6879</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6421</v>
+        <v>0.7331</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.1525</v>
+        <v>-0.0451</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2429,38 +2429,38 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5508</v>
+        <v>0.4329</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9061</v>
+        <v>0.8959</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1257</v>
+        <v>0.008</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7804</v>
+        <v>0.888</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2468,20 +2468,20 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1125</v>
+        <v>-0.1654</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7008</v>
+        <v>0.6847</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6488</v>
+        <v>0.7333</v>
       </c>
       <c r="L36" t="n">
-        <v>0.052</v>
+        <v>-0.0485</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2491,50 +2491,50 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1769</v>
+        <v>0.3815</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7936</v>
+        <v>0.8791</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7187</v>
+        <v>0.8661</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.1776</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4374</v>
+        <v>0.8062</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5991</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.1126</v>
+        <v>0.2071</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2543,38 +2543,38 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.96404592749758</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1858</v>
+        <v>0.1483</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6246</v>
+        <v>0.8774</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4913</v>
+        <v>0.0287</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1333</v>
+        <v>0.8487</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.0344</v>
+        <v>0.2091</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6992</v>
+        <v>0.8092</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6495</v>
+        <v>0.6005</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0497</v>
+        <v>0.2086</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2612,26 +2612,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1475</v>
+        <v>0.2377</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8238</v>
+        <v>0.9488</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0988</v>
+        <v>0.1226</v>
       </c>
       <c r="G39" t="n">
-        <v>0.725</v>
+        <v>0.8262</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>-0.0316</v>
+        <v>-0.0188</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.7022</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7145</v>
+        <v>0.7398</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0376</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2669,26 +2669,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2104</v>
+        <v>0.1128</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8185</v>
+        <v>0.7423</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0863</v>
+        <v>0.1316</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7322</v>
+        <v>0.6107</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>-0.0139</v>
+        <v>0.0353</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7902</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7121</v>
+        <v>0.6229</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.0916</v>
+        <v>0.1674</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2726,43 +2726,43 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1252</v>
+        <v>0.2019</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8027</v>
+        <v>0.9246</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1413</v>
+        <v>0.2076</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6614</v>
+        <v>0.717</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.0033</v>
+        <v>0.0934</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6288</v>
+        <v>0.6997</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7169</v>
+        <v>0.7373</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.0881</v>
+        <v>-0.0376</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2783,26 +2783,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2368</v>
+        <v>0.1666</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9446</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1597</v>
+        <v>0.1399</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6503</v>
+        <v>0.8047</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2810,87 +2810,1056 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>-0.0199</v>
+        <v>0.0599</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4115</v>
+        <v>0.7032</v>
       </c>
       <c r="K42" t="n">
-        <v>0.681</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.2694</v>
+        <v>0.0011</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8977000000000001</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>-0.0609</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.7368</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.86598189210379</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.86598189210379</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7003</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.5997</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8607</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.7177</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.7398</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8842</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>-0.0857</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.7736</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6506999999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.5999</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2084</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.4981</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.7247</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.86598189210379</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1215</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8256</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.1965</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.8022</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.2342</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6505</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.323</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>-0.1725</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8964</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.8884</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.5531</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.0648</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7183</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.8871</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.8452524630835619</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.1229</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.4688</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.6168</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>-0.0306</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.6278</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.7141</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-0.0863</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8792</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.8071</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.2264</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.545</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,19 +510,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3202</v>
+        <v>0.3081</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8939</v>
+        <v>0.918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0074</v>
+        <v>0.1096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8865</v>
+        <v>0.8084</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -530,20 +530,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.0533</v>
+        <v>-0.0376</v>
       </c>
       <c r="J2" t="n">
-        <v>0.767</v>
+        <v>0.7792</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5633</v>
+        <v>0.5931</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2037</v>
+        <v>0.1861</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -567,19 +567,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2267</v>
+        <v>0.1713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8777</v>
+        <v>0.755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0303</v>
+        <v>0.3102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8474</v>
+        <v>0.4449</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -587,20 +587,20 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.0011</v>
+        <v>-0.049</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7891</v>
+        <v>0.7749</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6081</v>
+        <v>0.638</v>
       </c>
       <c r="L3" t="n">
-        <v>0.181</v>
+        <v>0.1369</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -621,39 +621,39 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.940958804337006</v>
+        <v>0.066</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0713</v>
+        <v>0.1649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7866</v>
+        <v>0.8179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3453</v>
+        <v>0.1318</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4413</v>
+        <v>0.6861</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-0.1175</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1075</v>
+        <v>0.5235</v>
       </c>
       <c r="K4" t="n">
-        <v>0.438</v>
+        <v>0.3944</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3305</v>
+        <v>0.1291</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -681,19 +681,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2942</v>
+        <v>0.3696</v>
       </c>
       <c r="E5" t="n">
-        <v>0.895</v>
+        <v>0.9246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8867</v>
+        <v>0.8168</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1654</v>
+        <v>0.1272</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.615</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2086</v>
+        <v>0.1911</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -738,19 +738,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.940958804337006</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1115</v>
+        <v>0.1837</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0898</v>
+        <v>0.1485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7827</v>
+        <v>0.7083</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3912</v>
+        <v>0.4366</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6092</v>
+        <v>0.7687</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1602</v>
+        <v>0.1502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.449</v>
+        <v>0.6185</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -792,43 +792,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1004</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2041</v>
+        <v>0.8075</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7847</v>
+        <v>0.1323</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5806</v>
+        <v>0.6753</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.19</v>
+        <v>-0.1605</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.6128</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6135</v>
+        <v>0.8043</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1924</v>
+        <v>-0.1915</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -852,19 +852,19 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.940958804337006</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1032</v>
+        <v>0.1285</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9091</v>
+        <v>0.7402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.161</v>
+        <v>0.2036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7481</v>
+        <v>0.5366</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.2896</v>
+        <v>0.3467</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6097</v>
+        <v>0.7574</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1753</v>
+        <v>0.1716</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4343</v>
+        <v>0.5858</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2234</v>
+        <v>0.1088</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8088</v>
+        <v>0.6993</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0672</v>
+        <v>0.3244</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7416</v>
+        <v>0.375</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.0011</v>
+        <v>-0.0251</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0342</v>
+        <v>0.0106</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0954</v>
+        <v>0.1059</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0612</v>
+        <v>-0.0953</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -963,43 +963,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1956</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7721</v>
+        <v>0.3674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1134</v>
+        <v>0.6168</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6587</v>
+        <v>-0.2494</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.1197</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2273</v>
+        <v>0.4219</v>
       </c>
       <c r="K10" t="n">
-        <v>0.339</v>
+        <v>0.2997</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1117</v>
+        <v>0.1222</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -1023,19 +1023,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D11" t="n">
-        <v>0.444</v>
+        <v>0.4638</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0075</v>
+        <v>0.111</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8872</v>
+        <v>0.8136</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1043,20 +1043,20 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.0052</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7438</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7328</v>
+        <v>0.7126</v>
       </c>
       <c r="L11" t="n">
-        <v>0.011</v>
+        <v>0.0288</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -1080,19 +1080,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4431</v>
+        <v>0.4503</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8972</v>
+        <v>0.9255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0073</v>
+        <v>0.107</v>
       </c>
       <c r="G12" t="n">
-        <v>0.89</v>
+        <v>0.8185</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.2501</v>
+        <v>0.2045</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8089</v>
+        <v>0.8082</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5981</v>
+        <v>0.6159</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2108</v>
+        <v>0.1922</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1130,26 +1130,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.940958804337006</v>
+        <v>0.066</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1635</v>
+        <v>0.0164</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9241</v>
+        <v>0.5613</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1859</v>
+        <v>0.3262</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7382</v>
+        <v>0.2351</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-0.1441</v>
+        <v>-0.4468</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1031</v>
+        <v>0.0659</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7383</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6352</v>
+        <v>-0.7391</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1187,254 +1187,254 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0428</v>
+        <v>0.4816</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7708</v>
+        <v>0.9231</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3052</v>
+        <v>0.1101</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4656</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-0.4039</v>
+        <v>0.0008</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0342</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6692</v>
+        <v>0.6387</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.635</v>
+        <v>0.1329</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D15" t="n">
-        <v>0.449</v>
+        <v>0.2649</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8937</v>
+        <v>0.9248</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1166</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8858</v>
+        <v>0.8082</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-0.0159</v>
+        <v>-0.0673</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7901</v>
+        <v>0.7343</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6409</v>
+        <v>0.7146</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1491</v>
+        <v>0.0198</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.988503117170494</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2812</v>
+        <v>0.1831</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8942</v>
+        <v>0.8425</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1477</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8861</v>
+        <v>0.6948</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-0.1076</v>
+        <v>0.41</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6994</v>
+        <v>0.758</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7371</v>
+        <v>0.1673</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0377</v>
+        <v>0.5907</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.940958804337006</v>
+        <v>0.09</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1556</v>
+        <v>0.3454</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9142</v>
+        <v>0.926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1014</v>
+        <v>0.1128</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8128</v>
+        <v>0.8132</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2777</v>
+        <v>0.0814</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7794</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1628</v>
+        <v>0.6866</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4415</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.988503117170494</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3595</v>
+        <v>0.3525</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8949</v>
+        <v>0.8466</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008</v>
+        <v>0.0456</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8869</v>
+        <v>0.801</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.1534</v>
+        <v>0.4027</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8001</v>
+        <v>0.7563</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6466</v>
+        <v>0.1624</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1534</v>
+        <v>0.5939</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1472,43 +1472,43 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.940958804337006</v>
+        <v>0.09</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3168</v>
+        <v>0.2344</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9093</v>
+        <v>0.8711</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0496</v>
+        <v>0.145</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8597</v>
+        <v>0.7261</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3124</v>
+        <v>0.0313</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6056</v>
+        <v>0.7963</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1604</v>
+        <v>0.6586</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4452</v>
+        <v>0.1377</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1517,38 +1517,38 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2357</v>
+        <v>0.1969</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8474</v>
+        <v>0.7502</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0323</v>
+        <v>0.2754</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8151</v>
+        <v>0.4748</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1556,20 +1556,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.1401</v>
+        <v>-0.0694</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8038</v>
+        <v>0.7362</v>
       </c>
       <c r="K20" t="n">
-        <v>0.626</v>
+        <v>0.7084</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1778</v>
+        <v>0.0278</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1579,33 +1579,33 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1873</v>
+        <v>0.208</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7983</v>
+        <v>0.7749</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.264</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.5109</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1613,20 +1613,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.0391</v>
+        <v>-0.1462</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7163</v>
+        <v>0.3627</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7359</v>
+        <v>0.5593</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0197</v>
+        <v>-0.1966</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1636,90 +1636,90 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D22" t="n">
-        <v>0.221</v>
+        <v>0.4761</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.9179</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0599</v>
+        <v>0.1049</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7623</v>
+        <v>0.8131</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>-0.1993</v>
+        <v>0.172</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2439</v>
+        <v>0.8099</v>
       </c>
       <c r="K22" t="n">
-        <v>0.379</v>
+        <v>0.6214</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.135</v>
+        <v>0.1885</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4601</v>
+        <v>0.4605</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8948</v>
+        <v>0.9241</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0071</v>
+        <v>0.1074</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8877</v>
+        <v>0.8167</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2256</v>
+        <v>0.1741</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8017</v>
+        <v>0.8084</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.6196</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2165</v>
+        <v>0.1888</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1757,43 +1757,43 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4298</v>
+        <v>0.2554</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0077</v>
+        <v>0.118</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8879</v>
+        <v>0.7948</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2116</v>
+        <v>0.1075</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8038</v>
+        <v>0.7984</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5898</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.214</v>
+        <v>0.2011</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1802,55 +1802,55 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2427</v>
+        <v>0.4989</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8931</v>
+        <v>0.9221</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0083</v>
+        <v>0.1073</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8848</v>
+        <v>0.8148</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.098</v>
+        <v>0.2139</v>
       </c>
       <c r="J25" t="n">
-        <v>0.78</v>
+        <v>0.8064</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5702</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2098</v>
+        <v>0.192</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1859,38 +1859,38 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4728</v>
+        <v>0.3386</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8951</v>
+        <v>0.8368</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0065</v>
+        <v>0.218</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.6188</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.226</v>
+        <v>0.2019</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8101</v>
+        <v>0.7996</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6031</v>
+        <v>0.5999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.207</v>
+        <v>0.1997</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1928,43 +1928,43 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3781</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8758</v>
+        <v>0.8027</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0155</v>
+        <v>0.1378</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8602</v>
+        <v>0.6649</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1858</v>
+        <v>0.0655</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7867</v>
+        <v>0.4168</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5759</v>
+        <v>0.2887</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2109</v>
+        <v>0.128</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1973,55 +1973,55 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D28" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.4497</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9004</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1176</v>
+        <v>0.1022</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.8197</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.0258</v>
+        <v>0.121</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2457</v>
+        <v>0.8024</v>
       </c>
       <c r="K28" t="n">
-        <v>0.251</v>
+        <v>0.6039</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.0053</v>
+        <v>0.1985</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2030,38 +2030,38 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4393</v>
+        <v>0.3727</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8939</v>
+        <v>0.9131</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1236</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.7895</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2119</v>
+        <v>0.1603</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8062</v>
+        <v>0.8045</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5926</v>
+        <v>0.6101</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2136</v>
+        <v>0.1944</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2099,26 +2099,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3796</v>
+        <v>0.4094</v>
       </c>
       <c r="E30" t="n">
-        <v>0.891</v>
+        <v>0.9155</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01</v>
+        <v>0.1222</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8809</v>
+        <v>0.7933</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2126,16 +2126,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2374</v>
+        <v>0.1507</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8038</v>
+        <v>0.8074</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5894</v>
+        <v>0.6171</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2144</v>
+        <v>0.1903</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2156,26 +2156,26 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3991</v>
+        <v>0.3314</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8956</v>
+        <v>0.9214</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0086</v>
+        <v>0.1147</v>
       </c>
       <c r="G31" t="n">
-        <v>0.887</v>
+        <v>0.8067</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2107</v>
+        <v>0.0027</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8058</v>
+        <v>0.7864</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5946</v>
+        <v>0.6472</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2112</v>
+        <v>0.1393</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2213,140 +2213,140 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.988503117170494</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3534</v>
+        <v>-0.1492</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8966</v>
+        <v>0.5443</v>
       </c>
       <c r="F32" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8873</v>
+        <v>0.1763</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.03</v>
+        <v>-0.1896</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7996</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6478</v>
+        <v>0.7713</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1519</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1775</v>
+        <v>0.4694</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.9225</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3974</v>
+        <v>0.1061</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1103</v>
+        <v>0.8164</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.0674</v>
+        <v>-0.0688</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7679</v>
+        <v>0.681</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.7109</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0789</v>
+        <v>-0.0299</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4566</v>
+        <v>0.37</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8951</v>
+        <v>0.8358</v>
       </c>
       <c r="F34" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8871</v>
+        <v>0.6169</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.0936</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8097</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6142</v>
+        <v>0.6211</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1928</v>
+        <v>0.1886</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2384,100 +2384,100 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3339</v>
+        <v>0.1501</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8862</v>
+        <v>0.8518</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0207</v>
+        <v>0.1943</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8655</v>
+        <v>0.6575</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>-0.07439999999999999</v>
+        <v>0.1516</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6879</v>
+        <v>0.8055</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7331</v>
+        <v>0.6152</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.0451</v>
+        <v>0.1903</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4329</v>
+        <v>0.1091</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8959</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.008</v>
+        <v>0.1406</v>
       </c>
       <c r="G36" t="n">
-        <v>0.888</v>
+        <v>0.6583</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>-0.1654</v>
+        <v>0.0286</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6847</v>
+        <v>0.696</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7333</v>
+        <v>0.7352</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.0485</v>
+        <v>-0.0393</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2486,95 +2486,95 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3815</v>
+        <v>0.1515</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8791</v>
+        <v>0.6942</v>
       </c>
       <c r="F37" t="n">
-        <v>0.013</v>
+        <v>0.289</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8661</v>
+        <v>0.4052</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.1776</v>
+        <v>-0.0532</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8062</v>
+        <v>0.7825</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5991</v>
+        <v>0.6337</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2071</v>
+        <v>0.1489</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1483</v>
+        <v>0.1154</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8774</v>
+        <v>0.7715</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0287</v>
+        <v>0.1434</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8487</v>
+        <v>0.6281</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2582,20 +2582,20 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2091</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8092</v>
+        <v>0.6944</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6005</v>
+        <v>0.7202</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2086</v>
+        <v>-0.0258</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2605,33 +2605,33 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2377</v>
+        <v>0.1163</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9488</v>
+        <v>0.7911</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1226</v>
+        <v>0.1526</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8262</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2639,20 +2639,20 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>-0.0188</v>
+        <v>0.0492</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7022</v>
+        <v>0.6945</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7398</v>
+        <v>0.7274</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.0376</v>
+        <v>-0.0329</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2662,107 +2662,107 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1128</v>
+        <v>0.4243</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7423</v>
+        <v>0.9214</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1316</v>
+        <v>0.1121</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6107</v>
+        <v>0.8093</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.0353</v>
+        <v>0.0239</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7902</v>
+        <v>0.7377</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6229</v>
+        <v>0.7121</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1674</v>
+        <v>0.0256</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2019</v>
+        <v>0.4439</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9246</v>
+        <v>0.9265</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2076</v>
+        <v>0.1107</v>
       </c>
       <c r="G41" t="n">
-        <v>0.717</v>
+        <v>0.8158</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.0934</v>
+        <v>0.135</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6997</v>
+        <v>0.8065</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7373</v>
+        <v>0.6165</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.0376</v>
+        <v>0.1901</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2771,38 +2771,38 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1666</v>
+        <v>0.2239</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9446</v>
+        <v>0.7786</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1399</v>
+        <v>0.2778</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8047</v>
+        <v>0.5008</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2810,20 +2810,20 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.0599</v>
+        <v>0.0219</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7032</v>
+        <v>0.7308</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.7178</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0011</v>
+        <v>0.013</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2833,33 +2833,33 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3913</v>
+        <v>0.3934</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9231</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0071</v>
+        <v>0.106</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8905</v>
+        <v>0.8171</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2867,20 +2867,20 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>-0.0609</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7074</v>
+        <v>0.7325</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7368</v>
+        <v>0.721</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.0294</v>
+        <v>0.0115</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2890,54 +2890,54 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1806</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.6025</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1097</v>
+        <v>0.4327</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8395</v>
+        <v>0.1698</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.5856</v>
       </c>
       <c r="K44" t="n">
-        <v>0.697</v>
+        <v>0.8125</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0012</v>
+        <v>-0.2269</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2947,204 +2947,204 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2716</v>
+        <v>-0.0721</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9454</v>
+        <v>0.6968</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1199</v>
+        <v>0.3101</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8255</v>
+        <v>0.3867</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.0917</v>
+        <v>-0.0476</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7003</v>
+        <v>0.6791</v>
       </c>
       <c r="K45" t="n">
-        <v>0.706</v>
+        <v>0.7534</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.0056</v>
+        <v>-0.0743</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4014</v>
+        <v>0.1525</v>
       </c>
       <c r="E46" t="n">
-        <v>0.896</v>
+        <v>0.7981</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0074</v>
+        <v>0.1366</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8885</v>
+        <v>0.6615</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1853</v>
+        <v>-0.0626</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8089</v>
+        <v>0.6485</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5997</v>
+        <v>0.7967</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2092</v>
+        <v>-0.1482</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.988503117170494</v>
+        <v>0.066</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2514</v>
+        <v>0.0504</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8607</v>
+        <v>0.7685</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0281</v>
+        <v>0.1763</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8326</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.0145</v>
+        <v>0.0292</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7177</v>
+        <v>0.6974</v>
       </c>
       <c r="K47" t="n">
-        <v>0.7398</v>
+        <v>0.7268</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.0221</v>
+        <v>-0.0294</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3656</v>
+        <v>0.3807</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8922</v>
+        <v>0.9232</v>
       </c>
       <c r="F48" t="n">
-        <v>0.008</v>
+        <v>0.1082</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8842</v>
+        <v>0.8151</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3152,20 +3152,20 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>-0.0857</v>
+        <v>0.0028</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7736</v>
+        <v>0.7227</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6797</v>
+        <v>0.7169</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0939</v>
+        <v>0.0057</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3175,50 +3175,50 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1815</v>
+        <v>0.4603</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.9218</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3048</v>
+        <v>0.1081</v>
       </c>
       <c r="G49" t="n">
-        <v>0.346</v>
+        <v>0.8137</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1307</v>
+        <v>0.1292</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8083</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5999</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2084</v>
+        <v>0.1895</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3227,95 +3227,95 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1796</v>
+        <v>0.3558</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4981</v>
+        <v>0.9208</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4785</v>
+        <v>0.113</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0195</v>
+        <v>0.8078</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.045</v>
+        <v>-0.4042</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7489</v>
+        <v>0.1357</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7247</v>
+        <v>0.8076</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0242</v>
+        <v>-0.672</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.86598189210379</v>
+        <v>0.09</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2938</v>
+        <v>0.3277</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9234</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1215</v>
+        <v>0.1047</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8256</v>
+        <v>0.8188</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3323,16 +3323,16 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>-0.1965</v>
+        <v>0.1937</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.8078</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8022</v>
+        <v>0.6182</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.2342</v>
+        <v>0.1896</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3353,43 +3353,43 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.0121</v>
+        <v>0.4018</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3275</v>
+        <v>0.926</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6505</v>
+        <v>0.1096</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.323</v>
+        <v>0.8164</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>-0.1725</v>
+        <v>-0.0544</v>
       </c>
       <c r="J52" t="n">
-        <v>0.704</v>
+        <v>0.7339</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7418</v>
+        <v>0.7158</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.0378</v>
+        <v>0.0181</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3398,38 +3398,38 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3733</v>
+        <v>0.3831</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8964</v>
+        <v>0.9262</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0067</v>
+        <v>0.1083</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8897</v>
+        <v>0.8179</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3437,20 +3437,20 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>-0.0002</v>
+        <v>-0.3025</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7328</v>
+        <v>0.157</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7345</v>
+        <v>0.8044</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.0016</v>
+        <v>-0.6475</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3459,405 +3459,6 @@
         </is>
       </c>
       <c r="O53" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.4304</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.8884</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.1779</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.6037</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.2063</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.3627</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.8983</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.8919</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>-0.3644</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.1185</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.6716</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-0.5531</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.2897</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.8925</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.8851</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0.2144</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.8062</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.5933</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.2129</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.4021</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.8931</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.8857</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>-0.0648</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.7183</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.7443</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-0.026</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.3886</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.8947000000000001</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.8871</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>0.1886</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.8105</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.6015</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.2416</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.8792</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.0237</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.8555</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Peripheral</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>0.1955</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.8071</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.2102</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.988503117170494</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.3091</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.8944</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.8868</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>-0.2264</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.1232</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.6682</v>
-      </c>
-      <c r="L60" t="n">
-        <v>-0.545</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
         <is>
           <t>EnvWeak_TaxaStrong</t>
         </is>

--- a/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/artifacts/combined_robustness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,19 +510,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3081</v>
+        <v>0.3202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.918</v>
+        <v>0.8939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1096</v>
+        <v>0.0074</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8084</v>
+        <v>0.8865</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -530,20 +530,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-0.0376</v>
+        <v>0.0533</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7792</v>
+        <v>0.767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5931</v>
+        <v>0.5633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1861</v>
+        <v>0.2037</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
@@ -567,19 +567,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1713</v>
+        <v>0.2267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.755</v>
+        <v>0.8777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3102</v>
+        <v>0.0303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4449</v>
+        <v>0.8474</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -587,20 +587,20 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-0.049</v>
+        <v>0.0011</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7749</v>
+        <v>0.7891</v>
       </c>
       <c r="K3" t="n">
-        <v>0.638</v>
+        <v>0.6081</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1369</v>
+        <v>0.181</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -621,43 +621,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.066</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1649</v>
+        <v>-0.0713</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8179</v>
+        <v>0.7866</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1318</v>
+        <v>0.3453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6861</v>
+        <v>0.4413</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.1175</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5235</v>
+        <v>0.1075</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3944</v>
+        <v>0.438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1291</v>
+        <v>-0.3305</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -681,36 +681,36 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3696</v>
+        <v>0.2942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9246</v>
+        <v>0.895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1079</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8168</v>
+        <v>0.8867</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1272</v>
+        <v>0.1654</v>
       </c>
       <c r="J5" t="n">
-        <v>0.806</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.615</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1911</v>
+        <v>0.2086</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -719,12 +719,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -738,19 +738,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.870534508464975</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1837</v>
+        <v>0.1115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8568</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1485</v>
+        <v>0.0898</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7083</v>
+        <v>0.7827</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4366</v>
+        <v>0.3912</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7687</v>
+        <v>0.6092</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1502</v>
+        <v>0.1602</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6185</v>
+        <v>0.449</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -792,43 +792,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.1004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8075</v>
+        <v>0.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1323</v>
+        <v>0.7847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6753</v>
+        <v>-0.5806</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-0.1605</v>
+        <v>0.19</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6128</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8043</v>
+        <v>0.6135</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1915</v>
+        <v>0.1924</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -852,19 +852,19 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.870534508464975</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1285</v>
+        <v>0.1032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7402</v>
+        <v>0.9091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2036</v>
+        <v>0.161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5366</v>
+        <v>0.7481</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3467</v>
+        <v>0.2896</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7574</v>
+        <v>0.6097</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1716</v>
+        <v>0.1753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5858</v>
+        <v>0.4343</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1088</v>
+        <v>0.2234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6993</v>
+        <v>0.8088</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3244</v>
+        <v>0.0672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.375</v>
+        <v>0.7416</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-0.0251</v>
+        <v>0.0011</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0106</v>
+        <v>0.0342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1059</v>
+        <v>0.0954</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0953</v>
+        <v>-0.0612</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -963,43 +963,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.1956</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3674</v>
+        <v>0.7721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6168</v>
+        <v>0.1134</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2494</v>
+        <v>0.6587</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.1197</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4219</v>
+        <v>0.2273</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2997</v>
+        <v>0.339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1222</v>
+        <v>-0.1117</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
@@ -1023,19 +1023,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4638</v>
+        <v>0.444</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9247</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.111</v>
+        <v>0.0075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8136</v>
+        <v>0.8872</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7126</v>
+        <v>0.7328</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0288</v>
+        <v>0.011</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1080,19 +1080,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4503</v>
+        <v>0.4431</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9255</v>
+        <v>0.8972</v>
       </c>
       <c r="F12" t="n">
-        <v>0.107</v>
+        <v>0.0073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8185</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.2045</v>
+        <v>0.2501</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8082</v>
+        <v>0.8089</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6159</v>
+        <v>0.5981</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1922</v>
+        <v>0.2108</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1130,26 +1130,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.066</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0164</v>
+        <v>0.1635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5613</v>
+        <v>0.9241</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3262</v>
+        <v>0.1859</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2351</v>
+        <v>0.7382</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-0.4468</v>
+        <v>-0.1441</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0659</v>
+        <v>0.1031</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7383</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7391</v>
+        <v>-0.6352</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1187,100 +1187,100 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4816</v>
+        <v>0.0428</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9231</v>
+        <v>0.7708</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1101</v>
+        <v>0.3052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.4656</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.0008</v>
+        <v>-0.4039</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.0342</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6387</v>
+        <v>0.6692</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1329</v>
+        <v>-0.635</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2649</v>
+        <v>0.449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9248</v>
+        <v>0.8937</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1166</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8082</v>
+        <v>0.8858</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-0.0673</v>
+        <v>-0.0159</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7343</v>
+        <v>0.7901</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7146</v>
+        <v>0.6409</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0198</v>
+        <v>0.1491</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1289,38 +1289,38 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.870534508464975</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1831</v>
+        <v>0.2812</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8425</v>
+        <v>0.8942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1477</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6948</v>
+        <v>0.8861</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1328,20 +1328,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.41</v>
+        <v>-0.1076</v>
       </c>
       <c r="J16" t="n">
-        <v>0.758</v>
+        <v>0.6994</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1673</v>
+        <v>0.7371</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5907</v>
+        <v>-0.0377</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1351,90 +1351,90 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.09</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3454</v>
+        <v>0.1556</v>
       </c>
       <c r="E17" t="n">
-        <v>0.926</v>
+        <v>0.9142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1128</v>
+        <v>0.1014</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8132</v>
+        <v>0.8128</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.0814</v>
+        <v>0.2777</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7794</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6866</v>
+        <v>0.1628</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.4415</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.870534508464975</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3525</v>
+        <v>0.3595</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8466</v>
+        <v>0.8949</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0456</v>
+        <v>0.008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.801</v>
+        <v>0.8869</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1442,16 +1442,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4027</v>
+        <v>0.1534</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7563</v>
+        <v>0.8001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1624</v>
+        <v>0.6466</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5939</v>
+        <v>0.1534</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1472,43 +1472,43 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.09</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2344</v>
+        <v>0.3168</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8711</v>
+        <v>0.9093</v>
       </c>
       <c r="F19" t="n">
-        <v>0.145</v>
+        <v>0.0496</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7261</v>
+        <v>0.8597</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.0313</v>
+        <v>0.3124</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7963</v>
+        <v>0.6056</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6586</v>
+        <v>0.1604</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1377</v>
+        <v>0.4452</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1517,38 +1517,38 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1969</v>
+        <v>0.2357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7502</v>
+        <v>0.8474</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2754</v>
+        <v>0.0323</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4748</v>
+        <v>0.8151</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1556,20 +1556,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-0.0694</v>
+        <v>0.1401</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7362</v>
+        <v>0.8038</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7084</v>
+        <v>0.626</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0278</v>
+        <v>0.1778</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1579,33 +1579,33 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D21" t="n">
-        <v>0.208</v>
+        <v>0.1873</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7749</v>
+        <v>0.7983</v>
       </c>
       <c r="F21" t="n">
-        <v>0.264</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5109</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1613,20 +1613,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-0.1462</v>
+        <v>0.0391</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3627</v>
+        <v>0.7163</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5593</v>
+        <v>0.7359</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1966</v>
+        <v>-0.0197</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1636,90 +1636,90 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4761</v>
+        <v>0.221</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9179</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1049</v>
+        <v>0.0599</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8131</v>
+        <v>0.7623</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.172</v>
+        <v>-0.1993</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8099</v>
+        <v>0.2439</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6214</v>
+        <v>0.379</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1885</v>
+        <v>-0.135</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4605</v>
+        <v>0.4601</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9241</v>
+        <v>0.8948</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1074</v>
+        <v>0.0071</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8167</v>
+        <v>0.8877</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.1741</v>
+        <v>0.2256</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8084</v>
+        <v>0.8017</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6196</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1888</v>
+        <v>0.2165</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1757,43 +1757,43 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2554</v>
+        <v>0.4298</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.118</v>
+        <v>0.0077</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7948</v>
+        <v>0.8879</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.1075</v>
+        <v>0.2116</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7984</v>
+        <v>0.8038</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5898</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2011</v>
+        <v>0.214</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1802,55 +1802,55 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4989</v>
+        <v>0.2427</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9221</v>
+        <v>0.8931</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1073</v>
+        <v>0.0083</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8148</v>
+        <v>0.8848</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2139</v>
+        <v>0.098</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8064</v>
+        <v>0.78</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.5702</v>
       </c>
       <c r="L25" t="n">
-        <v>0.192</v>
+        <v>0.2098</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1859,38 +1859,38 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3386</v>
+        <v>0.4728</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8368</v>
+        <v>0.8951</v>
       </c>
       <c r="F26" t="n">
-        <v>0.218</v>
+        <v>0.0065</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6188</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2019</v>
+        <v>0.226</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7996</v>
+        <v>0.8101</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5999</v>
+        <v>0.6031</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1997</v>
+        <v>0.207</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1928,43 +1928,43 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.3781</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8027</v>
+        <v>0.8758</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1378</v>
+        <v>0.0155</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6649</v>
+        <v>0.8602</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.0655</v>
+        <v>0.1858</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4168</v>
+        <v>0.7867</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2887</v>
+        <v>0.5759</v>
       </c>
       <c r="L27" t="n">
-        <v>0.128</v>
+        <v>0.2109</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1973,55 +1973,55 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4497</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9004</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1022</v>
+        <v>0.1176</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8197</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.121</v>
+        <v>0.0258</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8024</v>
+        <v>0.2457</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6039</v>
+        <v>0.251</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1985</v>
+        <v>-0.0053</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2030,38 +2030,38 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3727</v>
+        <v>0.4393</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9131</v>
+        <v>0.8939</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1236</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7895</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.1603</v>
+        <v>0.2119</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8045</v>
+        <v>0.8062</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6101</v>
+        <v>0.5926</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1944</v>
+        <v>0.2136</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2099,26 +2099,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4094</v>
+        <v>0.3796</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9155</v>
+        <v>0.891</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1222</v>
+        <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7933</v>
+        <v>0.8809</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2126,16 +2126,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1507</v>
+        <v>0.2374</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8074</v>
+        <v>0.8038</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6171</v>
+        <v>0.5894</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1903</v>
+        <v>0.2144</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2156,26 +2156,26 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3314</v>
+        <v>0.3991</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9214</v>
+        <v>0.8956</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1147</v>
+        <v>0.0086</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8067</v>
+        <v>0.887</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.0027</v>
+        <v>0.2107</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7864</v>
+        <v>0.8058</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6472</v>
+        <v>0.5946</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1393</v>
+        <v>0.2112</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2213,140 +2213,140 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.870534508464975</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1492</v>
+        <v>0.3534</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5443</v>
+        <v>0.8966</v>
       </c>
       <c r="F32" t="n">
-        <v>0.368</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1763</v>
+        <v>0.8873</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>-0.1896</v>
+        <v>0.03</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.7996</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7713</v>
+        <v>0.6478</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.6929999999999999</v>
+        <v>0.1519</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4694</v>
+        <v>0.1775</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9225</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1061</v>
+        <v>0.3974</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8164</v>
+        <v>0.1103</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>-0.0688</v>
+        <v>0.0674</v>
       </c>
       <c r="J33" t="n">
-        <v>0.681</v>
+        <v>0.7679</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7109</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.0299</v>
+        <v>0.0789</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D34" t="n">
-        <v>0.37</v>
+        <v>0.4566</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8358</v>
+        <v>0.8951</v>
       </c>
       <c r="F34" t="n">
-        <v>0.219</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6169</v>
+        <v>0.8871</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8097</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6211</v>
+        <v>0.6142</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1886</v>
+        <v>0.1928</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2384,100 +2384,100 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1501</v>
+        <v>0.3339</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8518</v>
+        <v>0.8862</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1943</v>
+        <v>0.0207</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6575</v>
+        <v>0.8655</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1516</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8055</v>
+        <v>0.6879</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6152</v>
+        <v>0.7331</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1903</v>
+        <v>-0.0451</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1091</v>
+        <v>0.4329</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8959</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1406</v>
+        <v>0.008</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6583</v>
+        <v>0.888</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.0286</v>
+        <v>-0.1654</v>
       </c>
       <c r="J36" t="n">
-        <v>0.696</v>
+        <v>0.6847</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7352</v>
+        <v>0.7333</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.0393</v>
+        <v>-0.0485</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2486,95 +2486,95 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1515</v>
+        <v>0.3815</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6942</v>
+        <v>0.8791</v>
       </c>
       <c r="F37" t="n">
-        <v>0.289</v>
+        <v>0.013</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4052</v>
+        <v>0.8661</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-0.0532</v>
+        <v>0.1776</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7825</v>
+        <v>0.8062</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6337</v>
+        <v>0.5991</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1489</v>
+        <v>0.2071</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1154</v>
+        <v>0.1483</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7715</v>
+        <v>0.8774</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1434</v>
+        <v>0.0287</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6281</v>
+        <v>0.8487</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2582,20 +2582,20 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.2091</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6944</v>
+        <v>0.8092</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7202</v>
+        <v>0.6005</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.0258</v>
+        <v>0.2086</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2605,33 +2605,33 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1163</v>
+        <v>0.2377</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7911</v>
+        <v>0.9488</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1526</v>
+        <v>0.1226</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.8262</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.0492</v>
+        <v>-0.0188</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6945</v>
+        <v>0.7022</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7274</v>
+        <v>0.7398</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.0329</v>
+        <v>-0.0376</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2669,100 +2669,100 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4243</v>
+        <v>0.1128</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9214</v>
+        <v>0.7423</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1121</v>
+        <v>0.1316</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8093</v>
+        <v>0.6107</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.0239</v>
+        <v>0.0353</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7377</v>
+        <v>0.7902</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7121</v>
+        <v>0.6229</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0256</v>
+        <v>0.1674</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4439</v>
+        <v>0.2019</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9265</v>
+        <v>0.9246</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1107</v>
+        <v>0.2076</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8158</v>
+        <v>0.717</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.135</v>
+        <v>0.0934</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8065</v>
+        <v>0.6997</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6165</v>
+        <v>0.7373</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1901</v>
+        <v>-0.0376</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2771,38 +2771,38 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2239</v>
+        <v>0.1666</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7786</v>
+        <v>0.9446</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2778</v>
+        <v>0.1399</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5008</v>
+        <v>0.8047</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2810,20 +2810,20 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.0219</v>
+        <v>0.0599</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7308</v>
+        <v>0.7032</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7178</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>0.013</v>
+        <v>0.0011</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2833,33 +2833,33 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3934</v>
+        <v>0.3913</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9231</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0.106</v>
+        <v>0.0071</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8171</v>
+        <v>0.8905</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0609</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7325</v>
+        <v>0.7074</v>
       </c>
       <c r="K43" t="n">
-        <v>0.721</v>
+        <v>0.7368</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0115</v>
+        <v>-0.0294</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2897,47 +2897,47 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.1806</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6025</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4327</v>
+        <v>0.1097</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1698</v>
+        <v>0.8395</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>-0.0785</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5856</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8125</v>
+        <v>0.697</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.2269</v>
+        <v>0.0012</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2947,54 +2947,54 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0721</v>
+        <v>0.2716</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6968</v>
+        <v>0.9454</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3101</v>
+        <v>0.1199</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3867</v>
+        <v>0.8255</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>-0.0476</v>
+        <v>0.0917</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6791</v>
+        <v>0.7003</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7534</v>
+        <v>0.706</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.0743</v>
+        <v>-0.0056</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3004,90 +3004,90 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1525</v>
+        <v>0.4014</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7981</v>
+        <v>0.896</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1366</v>
+        <v>0.0074</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6615</v>
+        <v>0.8885</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>-0.0626</v>
+        <v>0.1853</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6485</v>
+        <v>0.8089</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7967</v>
+        <v>0.5997</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.1482</v>
+        <v>0.2092</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.066</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0504</v>
+        <v>0.2514</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7685</v>
+        <v>0.8607</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1763</v>
+        <v>0.0281</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.8326</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3095,20 +3095,20 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.0292</v>
+        <v>0.0145</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6974</v>
+        <v>0.7177</v>
       </c>
       <c r="K47" t="n">
-        <v>0.7268</v>
+        <v>0.7398</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.0294</v>
+        <v>-0.0221</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3118,33 +3118,33 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3807</v>
+        <v>0.3656</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9232</v>
+        <v>0.8922</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1082</v>
+        <v>0.008</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8151</v>
+        <v>0.8842</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3152,16 +3152,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.0028</v>
+        <v>-0.0857</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7227</v>
+        <v>0.7736</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7169</v>
+        <v>0.6797</v>
       </c>
       <c r="L48" t="n">
-        <v>0.0057</v>
+        <v>0.0939</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3182,43 +3182,43 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4603</v>
+        <v>0.1815</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9218</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1081</v>
+        <v>0.3048</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8137</v>
+        <v>0.346</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1292</v>
+        <v>0.1307</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8083</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5999</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1895</v>
+        <v>0.2084</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3227,169 +3227,169 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3558</v>
+        <v>0.1796</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9208</v>
+        <v>0.4981</v>
       </c>
       <c r="F50" t="n">
-        <v>0.113</v>
+        <v>0.4785</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8078</v>
+        <v>0.0195</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>-0.4042</v>
+        <v>0.045</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1357</v>
+        <v>0.7489</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8076</v>
+        <v>0.7247</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.672</v>
+        <v>0.0242</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3277</v>
+        <v>0.2938</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9234</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1047</v>
+        <v>0.1215</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8188</v>
+        <v>0.8256</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.1937</v>
+        <v>-0.1965</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8078</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6182</v>
+        <v>0.8022</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1896</v>
+        <v>-0.2342</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4018</v>
+        <v>-0.0121</v>
       </c>
       <c r="E52" t="n">
-        <v>0.926</v>
+        <v>0.3275</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1096</v>
+        <v>0.6505</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8164</v>
+        <v>-0.323</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>-0.0544</v>
+        <v>-0.1725</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7339</v>
+        <v>0.704</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7158</v>
+        <v>0.7418</v>
       </c>
       <c r="L52" t="n">
-        <v>0.0181</v>
+        <v>-0.0378</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3398,67 +3398,466 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8964</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.8884</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8919</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.3644</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1185</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.5531</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8857</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.0648</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7183</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.8871</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1886</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8792</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.8071</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.3831</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.9262</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.1083</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.8179</v>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.988503117170494</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>-0.3025</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.8044</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-0.6475</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="I60" t="n">
+        <v>-0.2264</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.545</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
         <is>
           <t>EnvWeak_TaxaStrong</t>
         </is>
